--- a/docs/deliverables/04_テスト/勤怠管理システム_テスト仕様書兼実施結果_v1.2.xlsx
+++ b/docs/deliverables/04_テスト/勤怠管理システム_テスト仕様書兼実施結果_v1.2.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙・サマリー" sheetId="1" r:id="Ra95cda8389454eea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="環境・起動" sheetId="2" r:id="Rf61cdb5b8efd4e03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証・パスワード" sheetId="3" r:id="Re6d3d6eafae841a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム・ナビ" sheetId="4" r:id="R3f461052495d468b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勤務表入力" sheetId="5" r:id="R9de15ef81b084ddd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="計算・集計" sheetId="6" r:id="Rcf115135e77247c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="過去勤怠" sheetId="7" r:id="Rbafa1a6a89ae4e27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="権限・管理" sheetId="8" r:id="Rc4d630dd5cd44e6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="その他" sheetId="9" r:id="R78b0f78833be4a76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ファイル取込" sheetId="10" r:id="Rae99f5aebfc04958"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部連携" sheetId="11" r:id="Re5bc06ad3df0426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="端末・印刷" sheetId="12" r:id="R3cc0e11298b44e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セキュリティ" sheetId="13" r:id="R79947c86c8384cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="回帰確認" sheetId="14" r:id="R35c63e514ac148ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excel照合" sheetId="15" r:id="Re946df22f776467c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト環境・データ" sheetId="16" r:id="Rccc5c47bba9140b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不具合記録" sheetId="17" r:id="R394834b05c854cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙・サマリー" sheetId="1" r:id="Ra75fccd7dc894999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="環境・起動" sheetId="2" r:id="Reacba11f91754d12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証・パスワード" sheetId="3" r:id="Rd2145ea682304a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム・ナビ" sheetId="4" r:id="R3f04f7e6912846e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勤務表入力" sheetId="5" r:id="Rbe0f1fb22c9f42e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="計算・集計" sheetId="6" r:id="R39683cfd39604e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="過去勤怠" sheetId="7" r:id="Re995e24ab6064780"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="権限・管理" sheetId="8" r:id="R83c40c8c994f4bc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="その他" sheetId="9" r:id="Ra510fe0314c24fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ファイル取込" sheetId="10" r:id="Ra643d2697f764ac1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部連携" sheetId="11" r:id="Ra901242b8c284076"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="端末・印刷" sheetId="12" r:id="R71d2449ed6db498c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セキュリティ" sheetId="13" r:id="Ra0fb38eee11a43b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="回帰確認" sheetId="14" r:id="R854c87c7395f44f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excel照合" sheetId="15" r:id="R8931c20b9ab1459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト環境・データ" sheetId="16" r:id="R5cb3015b352a44c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不具合記録" sheetId="17" r:id="R76e5e9555dba48bd"/>
   </x:sheets>
 </x:workbook>
 </file>
